--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="500">
   <si>
     <t>Filename</t>
   </si>
@@ -811,16 +811,22 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9818,0.0011,0.0104,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0120,0.0001,0.0000,0.9971</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9953,0.0008,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0332,0.0000,0.0000,0.9945</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
@@ -829,664 +835,685 @@
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0009,0.0002,0.0001</t>
+    <t>0.9988,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0002,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0350,0.0006,0.9746,0.0000</t>
+  </si>
+  <si>
+    <t>0.0106,0.0007,0.9904,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.1693,0.8344,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8179,0.0181,0.0994,0.0025</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9989,0.0008</t>
+  </si>
+  <si>
+    <t>0.0321,0.0001,0.9793,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0708,0.9283,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9548,0.0130,0.0145,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9987,0.0036</t>
+  </si>
+  <si>
+    <t>0.0043,0.9899,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.9174,0.0794,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0596,0.0019,0.9440,0.0017</t>
+  </si>
+  <si>
+    <t>0.1584,0.8887,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.9929,0.0126,0.0010</t>
+  </si>
+  <si>
+    <t>0.0286,0.9124,0.0254,0.0054</t>
+  </si>
+  <si>
+    <t>0.0007,0.0104,0.9947,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0021,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0550,0.0000,0.9157,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9658,0.0004,0.8437</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0695,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0015,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9620,0.9798,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0011,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.9956,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8899,0.0029,0.1277,0.0000</t>
+  </si>
+  <si>
+    <t>0.9704,0.0133,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9743,0.9252,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0155,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.6309,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0086,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.5877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9894,0.9450,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9809,0.9931,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9878,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.6538,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0058,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9919,0.0063,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0041,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9866,0.0026,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0022,0.9933,0.0008</t>
-  </si>
-  <si>
-    <t>0.7784,0.0008,0.3008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.5192,0.5202,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9985,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9334,0.0003,0.0746,0.0002</t>
-  </si>
-  <si>
-    <t>0.7583,0.0086,0.1743,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0117,0.9952,0.0004</t>
-  </si>
-  <si>
-    <t>0.0100,0.0002,0.9933,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.6783,0.2424,0.0094,0.0005</t>
-  </si>
-  <si>
-    <t>0.9860,0.0059,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9994,0.0022</t>
-  </si>
-  <si>
-    <t>0.0020,0.9621,0.0756,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0012,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0010,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.1461,0.8945,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.9927,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0203,0.9497,0.0170,0.0067</t>
-  </si>
-  <si>
-    <t>0.0133,0.0014,0.9686,0.0032</t>
-  </si>
-  <si>
-    <t>0.0160,0.0017,0.9762,0.0010</t>
-  </si>
-  <si>
-    <t>0.0142,0.0001,0.9849,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.0070,0.9830,0.0005</t>
-  </si>
-  <si>
-    <t>0.0330,0.9220,0.0093,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0012,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.6614,0.0003,0.8597</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3865,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0007,0.9973,0.0011</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0275,0.0003,0.9832,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0050,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9251,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0027,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.9990,0.0000</t>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9767,0.0391,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0108,0.0210,0.9673,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9980,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9986,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1579,0.8518,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0476,0.0083,0.9274,0.0036</t>
+  </si>
+  <si>
+    <t>0.9697,0.0003,0.0366,0.0000</t>
+  </si>
+  <si>
+    <t>0.9138,0.0041,0.0581,0.0004</t>
+  </si>
+  <si>
+    <t>0.5683,0.0012,0.4189,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0968,0.0004,0.9968</t>
+  </si>
+  <si>
+    <t>0.0006,0.9996,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0036,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9976,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.8929,0.0810,0.0131,0.0002</t>
+  </si>
+  <si>
+    <t>0.0625,0.9053,0.0087,0.0008</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6011,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.6327,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0868,0.0046,0.9230,0.0001</t>
+  </si>
+  <si>
+    <t>0.3681,0.0264,0.5774,0.0022</t>
+  </si>
+  <si>
+    <t>0.0543,0.0001,0.9670,0.0001</t>
+  </si>
+  <si>
+    <t>0.9886,0.0017,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.1922,0.0000,0.0000,0.9573</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9092,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9974,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0788,0.9209,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5382,0.0000,0.0002,0.6875</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0566,0.0155,0.9364,0.0030</t>
+  </si>
+  <si>
+    <t>0.9956,0.0001,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9839,0.0081,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.1210,0.8532,0.0057,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0299,0.9531,0.0074,0.0002</t>
+  </si>
+  <si>
+    <t>0.9791,0.0094,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0013,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2687,0.7712,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.5517,0.4143,0.0109,0.0002</t>
+  </si>
+  <si>
+    <t>0.8524,0.1801,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.6782,0.9370,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0086,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9845,0.0094,0.0042,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5153,0.6543,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9876,0.0073,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.9961,0.0014</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.0688,0.0024,0.9502,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0032,0.9952,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0238,0.0122,0.9714,0.0004</t>
-  </si>
-  <si>
-    <t>0.9122,0.0975,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0009,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9736,0.9551,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0315,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.7238,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0009,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.3582,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9757,0.8710,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.4855,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9651,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.7826,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0037,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0050,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0021,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0026,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0257,0.0044,0.9762,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9980,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9977,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1764,0.8579,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.3197,0.0016,0.6136,0.0031</t>
-  </si>
-  <si>
-    <t>0.4350,0.0005,0.6735,0.0001</t>
-  </si>
-  <si>
-    <t>0.3640,0.0348,0.2504,0.0059</t>
-  </si>
-  <si>
-    <t>0.9441,0.0014,0.0396,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0098,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0160,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8397,0.1017,0.0213,0.0002</t>
-  </si>
-  <si>
-    <t>0.5813,0.3536,0.0136,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.8722,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2031,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0003,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.9169,0.0234,0.0293,0.0026</t>
-  </si>
-  <si>
-    <t>0.0556,0.0002,0.9514,0.0007</t>
-  </si>
-  <si>
-    <t>0.9283,0.0016,0.0508,0.0011</t>
-  </si>
-  <si>
-    <t>0.1124,0.0000,0.0000,0.9798</t>
-  </si>
-  <si>
-    <t>0.0000,0.0046,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9823,0.9782,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9947,0.0011,0.0032</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0796,0.9231,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1329,0.0000,0.0002,0.9621</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0712,0.0129,0.9354,0.0014</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9273,0.1061,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9898,0.0085,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.6447,0.3616,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9555,0.0255,0.0088,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0007,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0040,0.0008,0.0011</t>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0080,0.0082,0.9645,0.0012</t>
+  </si>
+  <si>
+    <t>0.0265,0.0008,0.9713,0.0008</t>
+  </si>
+  <si>
+    <t>0.0028,0.2501,0.7114,0.0014</t>
+  </si>
+  <si>
+    <t>0.0047,0.0171,0.9868,0.0002</t>
+  </si>
+  <si>
+    <t>0.1335,0.0147,0.8047,0.0010</t>
+  </si>
+  <si>
+    <t>0.8462,0.0306,0.0399,0.0013</t>
+  </si>
+  <si>
+    <t>0.9880,0.0005,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.6544,0.0220,0.1737,0.0034</t>
+  </si>
+  <si>
+    <t>0.0127,0.9900,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9989,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0826,0.9347,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.1255,0.9076,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9975,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6589,0.4505,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9917,0.0001,0.0069,0.0000</t>
+  </si>
+  <si>
+    <t>0.9872,0.0027,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.9314,0.0011,0.0685,0.0003</t>
+  </si>
+  <si>
+    <t>0.2148,0.0005,0.8053,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9995,0.0027</t>
+  </si>
+  <si>
+    <t>0.0088,0.0143,0.9610,0.0027</t>
+  </si>
+  <si>
+    <t>0.0020,0.1102,0.9686,0.0010</t>
+  </si>
+  <si>
+    <t>0.0027,0.0003,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1489,0.9733,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0018,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0020,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0003,0.0009</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0324,0.9718,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.3440,0.5160,0.0254,0.0006</t>
-  </si>
-  <si>
-    <t>0.9273,0.0831,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.1792,0.2659,0.5332,0.0007</t>
-  </si>
-  <si>
-    <t>0.9904,0.0109,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.2591,0.7994,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9633,0.0076,0.0184,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.9977,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9982,0.0007</t>
-  </si>
-  <si>
-    <t>0.0188,0.0113,0.9767,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0032,0.9942,0.0006</t>
-  </si>
-  <si>
-    <t>0.0175,0.0006,0.9869,0.0001</t>
-  </si>
-  <si>
-    <t>0.0122,0.5801,0.2134,0.0017</t>
-  </si>
-  <si>
-    <t>0.1275,0.0194,0.7975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0259,0.0817,0.8281,0.0002</t>
-  </si>
-  <si>
-    <t>0.1517,0.0061,0.8078,0.0005</t>
-  </si>
-  <si>
-    <t>0.9558,0.0012,0.0295,0.0009</t>
-  </si>
-  <si>
-    <t>0.9133,0.0205,0.0287,0.0004</t>
-  </si>
-  <si>
-    <t>0.0141,0.9892,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9983,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1176,0.8831,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.1366,0.9005,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9976,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9763,0.0202,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9932,0.0002,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9837,0.0009,0.0080,0.0001</t>
-  </si>
-  <si>
-    <t>0.9429,0.0003,0.0553,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.1262,0.9853,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.7750,0.6227,0.0017</t>
-  </si>
-  <si>
-    <t>0.0038,0.0015,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0016,0.0002,0.0005</t>
+    <t>0.0007,0.0071,0.9983,0.0036</t>
+  </si>
+  <si>
+    <t>0.0096,0.0325,0.9433,0.0015</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0433,0.9800,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0167,0.0014,0.9823,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.0000,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0005,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0109,0.9915,0.0008</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8509,0.0001,0.1676,0.0005</t>
+  </si>
+  <si>
+    <t>0.9021,0.0006,0.0920,0.0009</t>
+  </si>
+  <si>
+    <t>0.9937,0.0055,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0026,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0026,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9968,0.0023,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0024,0.9986,0.0005</t>
-  </si>
-  <si>
-    <t>0.0155,0.7497,0.0808,0.0039</t>
-  </si>
-  <si>
-    <t>0.9956,0.0008,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.2281,0.9575,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.1373,0.0015,0.8911,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0020,0.9885,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0190,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.9916,0.0001,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.9867,0.0001,0.0101,0.0000</t>
-  </si>
-  <si>
-    <t>0.9834,0.0006,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.0035,0.9873,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0048,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0120,0.9652,0.0005</t>
-  </si>
-  <si>
-    <t>0.0318,0.0161,0.8559,0.0052</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1301,0.0045,0.7641,0.0162</t>
-  </si>
-  <si>
-    <t>0.0264,0.0058,0.9510,0.0018</t>
-  </si>
-  <si>
-    <t>0.1032,0.0016,0.8385,0.0162</t>
-  </si>
-  <si>
-    <t>0.9394,0.0000,0.0013,0.0362</t>
-  </si>
-  <si>
-    <t>0.0069,0.0055,0.0003,0.9941</t>
-  </si>
-  <si>
-    <t>0.0050,0.0001,0.0039,0.9964</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7393,0.0184,0.0010,0.1355</t>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.0049,0.9821,0.0021</t>
+  </si>
+  <si>
+    <t>0.2151,0.0069,0.7219,0.0019</t>
+  </si>
+  <si>
+    <t>0.0141,0.0012,0.9700,0.0154</t>
+  </si>
+  <si>
+    <t>0.0148,0.0032,0.9738,0.0012</t>
+  </si>
+  <si>
+    <t>0.1162,0.0003,0.8534,0.0015</t>
+  </si>
+  <si>
+    <t>0.9801,0.0000,0.0004,0.0154</t>
+  </si>
+  <si>
+    <t>0.0010,0.0017,0.0002,0.9990</t>
+  </si>
+  <si>
+    <t>0.0398,0.0001,0.0018,0.9872</t>
+  </si>
+  <si>
+    <t>0.9174,0.0129,0.0005,0.0177</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1899,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1886,7 +1913,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,7 +1927,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1914,7 +1941,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1928,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1942,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1956,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1984,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1998,7 +2025,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2012,7 +2039,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2065,7 +2092,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>279</v>
@@ -2096,7 +2123,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2110,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2124,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2138,7 +2165,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2152,7 +2179,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2166,7 +2193,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,7 +2207,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2194,7 +2221,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2208,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2222,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,7 +2263,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2250,7 +2277,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2275,7 +2302,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2345,7 +2372,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2516,7 +2543,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2698,7 +2725,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>272</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2739,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2753,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2767,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2781,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2795,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2809,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2823,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2837,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2821,10 +2848,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,7 +2865,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2879,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,7 +2893,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2880,7 +2907,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2894,7 +2921,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,7 +2935,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2949,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2963,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2977,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2991,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +3005,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +3019,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3003,10 +3030,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,7 +3047,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3061,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,10 +3072,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3062,7 +3089,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,7 +3103,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3118,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3132,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3146,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3160,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3174,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3188,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3202,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3216,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3230,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3244,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3258,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3272,7 +3299,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3286,7 +3313,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3355,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,7 +3369,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3383,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3384,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3398,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3412,7 +3439,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3426,7 +3453,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3440,7 +3467,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,7 +3481,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,7 +3495,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,10 +3506,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,7 +3523,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,7 +3537,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,7 +3551,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3538,7 +3565,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3552,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3566,7 +3593,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3607,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3621,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3619,10 +3646,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3678,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3692,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3733,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3747,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3761,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,7 +3775,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,10 +3786,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3803,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3817,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3815,10 +3842,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,7 +3859,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,7 +3873,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3901,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3915,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3929,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3943,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3957,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3971,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3985,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,7 +3999,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +4013,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3997,10 +4024,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4055,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,10 +4094,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,10 +4136,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4126,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4168,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4182,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4196,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4210,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4224,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4265,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>414</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,7 +4293,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,10 +4304,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4305,10 +4332,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4322,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4336,7 +4363,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4350,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,10 +4388,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D180" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4378,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4392,7 +4419,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4406,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4434,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4462,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4476,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4490,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4504,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,7 +4545,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,10 +4556,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,7 +4573,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,7 +4587,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,10 +4598,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4588,7 +4615,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,7 +4629,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,7 +4643,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4630,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,7 +4671,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,7 +4685,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,7 +4699,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4686,7 +4713,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4727,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4741,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,7 +4755,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4739,10 +4766,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4781,10 +4808,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4825,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4839,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4923,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>415</v>
+        <v>359</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4937,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4924,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,10 +4976,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4993,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +5021,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5077,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5091,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5105,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>415</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5231,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5245,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5259,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>482</v>
+        <v>434</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,7 +5343,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,7 +5357,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5371,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5385,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5413,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5427,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5441,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>489</v>
+        <v>399</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,7 +5455,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
